--- a/results/phase1_detailed.xlsx
+++ b/results/phase1_detailed.xlsx
@@ -492,28 +492,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13777.54851491904</v>
+        <v>14845.90227742464</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009030818939208984</v>
+        <v>0.009436607360839844</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>13502.12178552473</v>
+        <v>16441.74136790568</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06995844841003418</v>
+        <v>0.07339000701904297</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16057.19069281593</v>
+        <v>16104.12734994348</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01047444343566895</v>
+        <v>0.009662866592407227</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>13366.47699680607</v>
+        <v>16292.72322848368</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06458234786987305</v>
+        <v>0.08521699905395508</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -563,26 +563,28 @@
           <t>C103</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>16133.68269800485</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01134371757507324</v>
+        <v>0.01047682762145996</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>11135.09987767372</v>
+        <v>15171.02028995063</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0771481990814209</v>
+        <v>0.1079645156860352</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -599,29 +601,31 @@
           <t>C104</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>14821.49517334907</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01389002799987793</v>
+        <v>0.01268720626831055</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>11360.51875553155</v>
+        <v>12555.73672352827</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1089777946472168</v>
+        <v>0.1245648860931396</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +640,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14727.52475617427</v>
+        <v>13765.99267549346</v>
       </c>
       <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01054072380065918</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15493.84230044368</v>
+      </c>
+      <c r="H6" t="n">
         <v>13</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.0120539665222168</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10939.08214623804</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
       <c r="I6" t="n">
-        <v>0.06511068344116211</v>
+        <v>0.07410383224487305</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -672,25 +676,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13847.44873437232</v>
+        <v>14764.74073186027</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009838581085205078</v>
+        <v>0.009588479995727539</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>12082.36371744783</v>
+        <v>15549.20219978505</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.115854024887085</v>
+        <v>0.07533001899719238</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -708,28 +712,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13854.28483159617</v>
+        <v>14004.48982032785</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009630680084228516</v>
+        <v>0.01011204719543457</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>12194.1688124894</v>
+        <v>14175.45388655194</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06785130500793457</v>
+        <v>0.0814666748046875</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -744,25 +748,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13656.88140160404</v>
+        <v>12768.65945763432</v>
       </c>
       <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01004815101623535</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14270.76657457749</v>
+      </c>
+      <c r="H9" t="n">
         <v>12</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01055407524108887</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12539.58842028736</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.06435585021972656</v>
+        <v>0.08692669868469238</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -780,25 +784,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12627.95142527504</v>
+        <v>13742.45511022038</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01067352294921875</v>
+        <v>0.01069808006286621</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>11458.81721062877</v>
+        <v>11414.99902326231</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07547092437744141</v>
+        <v>0.1018385887145996</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -816,25 +820,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6714.450936983898</v>
+        <v>6491.638117296146</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01067543029785156</v>
+        <v>0.01660823822021484</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>3660.83110722045</v>
+        <v>5491.345256994378</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2673749923706055</v>
+        <v>0.3735225200653076</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -852,25 +856,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7834.364581952286</v>
+        <v>7204.537560059012</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01109600067138672</v>
+        <v>0.01016950607299805</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>4996.003638193533</v>
+        <v>5213.535070367382</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3083631992340088</v>
+        <v>0.4315547943115234</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -888,25 +892,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6763.421507738411</v>
+        <v>6998.81889369757</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01306629180908203</v>
+        <v>0.01155757904052734</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>4861.279158000177</v>
+        <v>5669.335548475327</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3493435382843018</v>
+        <v>0.5116252899169922</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -924,28 +928,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6508.67603901192</v>
+        <v>6598.869277270063</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01254510879516602</v>
+        <v>0.0123600959777832</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>5476.161142805679</v>
+        <v>5626.896654944936</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4281048774719238</v>
+        <v>0.800128698348999</v>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -960,25 +964,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5563.997820220503</v>
+        <v>5380.500314890749</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01039695739746094</v>
+        <v>0.01433777809143066</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3758.154333859991</v>
+        <v>5006.785508832825</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2678322792053223</v>
+        <v>0.3820834159851074</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -996,25 +1000,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5134.683621817112</v>
+        <v>5487.852245234219</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01042389869689941</v>
+        <v>0.01158380508422852</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>4837.978790580004</v>
+        <v>4972.294963558592</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2724549770355225</v>
+        <v>0.4088253974914551</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -1032,25 +1036,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6101.527714333875</v>
+        <v>5331.977777677878</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01047468185424805</v>
+        <v>0.01254034042358398</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3680.895541933724</v>
+        <v>5107.245706830425</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3150110244750977</v>
+        <v>0.4051306247711182</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -1068,28 +1072,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5300.068982784745</v>
+        <v>5126.163780499669</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01500773429870605</v>
+        <v>0.01082515716552734</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3870.399323359628</v>
+        <v>5178.439255134228</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3127133846282959</v>
+        <v>0.4309237003326416</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1112,22 +1116,22 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.008462429046630859</v>
+        <v>0.00915980339050293</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>24306.08763307427</v>
+        <v>26344.11626615825</v>
       </c>
       <c r="H19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03716158866882324</v>
+        <v>0.04046344757080078</v>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1150,22 +1154,22 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01004385948181152</v>
+        <v>0.009358406066894531</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>23224.30663623398</v>
+        <v>25241.44064036839</v>
       </c>
       <c r="H20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I20" t="n">
-        <v>0.05082011222839355</v>
+        <v>0.0654759407043457</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1188,22 +1192,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01104331016540527</v>
+        <v>0.01020503044128418</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>17826.29257771969</v>
+        <v>18868.23702374467</v>
       </c>
       <c r="H21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05911731719970703</v>
+        <v>0.07220697402954102</v>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1226,22 +1230,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0112459659576416</v>
+        <v>0.01183009147644043</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>14648.77478909665</v>
+        <v>14486.64718832978</v>
       </c>
       <c r="H22" t="n">
         <v>13</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07224559783935547</v>
+        <v>0.09750962257385254</v>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1264,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.009810686111450195</v>
+        <v>0.008955240249633789</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>19030.69799740824</v>
+        <v>21142.45502866075</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04793787002563477</v>
+        <v>0.05565428733825684</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1302,22 +1306,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01119422912597656</v>
+        <v>0.009627342224121094</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>17930.20951802103</v>
+        <v>20058.43370294574</v>
       </c>
       <c r="H24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I24" t="n">
-        <v>0.05446052551269531</v>
+        <v>0.06709480285644531</v>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1340,22 +1344,22 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01044321060180664</v>
+        <v>0.01040911674499512</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>15602.51409277013</v>
+        <v>16815.85393608709</v>
       </c>
       <c r="H25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" t="n">
-        <v>0.06170773506164551</v>
+        <v>0.08148455619812012</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1378,22 +1382,22 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01180148124694824</v>
+        <v>0.01181387901306152</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>13408.90087252276</v>
+        <v>14426.56252083727</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07605981826782227</v>
+        <v>0.1053345203399658</v>
       </c>
       <c r="J26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1416,22 +1420,22 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01053667068481445</v>
+        <v>0.009766817092895508</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>16822.47657739008</v>
+        <v>18944.48576580587</v>
       </c>
       <c r="H27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I27" t="n">
-        <v>0.05391407012939453</v>
+        <v>0.06923770904541016</v>
       </c>
       <c r="J27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1454,22 +1458,22 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01074028015136719</v>
+        <v>0.01071071624755859</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>14614.69133008363</v>
+        <v>16754.19319245737</v>
       </c>
       <c r="H28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05716991424560547</v>
+        <v>0.08009719848632812</v>
       </c>
       <c r="J28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1492,22 +1496,22 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01024961471557617</v>
+        <v>0.01440787315368652</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>14491.42975617113</v>
+        <v>16719.2709864069</v>
       </c>
       <c r="H29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.06438493728637695</v>
+        <v>0.08121275901794434</v>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1530,22 +1534,22 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01156735420227051</v>
+        <v>0.0120234489440918</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>13419.41069607827</v>
+        <v>15670.21143305496</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07616472244262695</v>
+        <v>0.1019420623779297</v>
       </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1559,28 +1563,26 @@
           <t>R201</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="C31" t="n">
+        <v>8400.325090392653</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.009989023208618164</v>
+        <v>0.01032590866088867</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>6875.096284348413</v>
+        <v>7087.683497077942</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3043584823608398</v>
+        <v>0.4182214736938477</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -1598,28 +1600,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7135.776923944524</v>
+        <v>9422.945092653354</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01077771186828613</v>
+        <v>0.010650634765625</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>6874.72146767336</v>
+        <v>5723.192131849955</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4262716770172119</v>
+        <v>0.6250205039978027</v>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1633,28 +1635,26 @@
           <t>R203</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="C33" t="n">
+        <v>6909.43665669443</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01115775108337402</v>
+        <v>0.01126194000244141</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>5710.280768525544</v>
+        <v>5833.337047371457</v>
       </c>
       <c r="H33" t="n">
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5514216423034668</v>
+        <v>0.7392818927764893</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
@@ -1680,22 +1680,22 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01241159439086914</v>
+        <v>0.01218247413635254</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>5319.566144561675</v>
+        <v>5207.49300904482</v>
       </c>
       <c r="H34" t="n">
         <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8533952236175537</v>
+        <v>1.032096147537231</v>
       </c>
       <c r="J34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1710,28 +1710,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5718.705455338226</v>
+        <v>6826.740131651293</v>
       </c>
       <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.01147055625915527</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5702.256050563352</v>
+      </c>
+      <c r="H35" t="n">
         <v>4</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.01426053047180176</v>
-      </c>
-      <c r="F35" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4543.892544039079</v>
-      </c>
-      <c r="H35" t="n">
-        <v>3</v>
-      </c>
       <c r="I35" t="n">
-        <v>0.4754292964935303</v>
+        <v>0.6705715656280518</v>
       </c>
       <c r="J35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1746,25 +1746,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5752.537341187453</v>
+        <v>6811.102874081127</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01245284080505371</v>
+        <v>0.01122045516967773</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>4421.008773174271</v>
+        <v>4486.918915866073</v>
       </c>
       <c r="H36" t="n">
         <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5822899341583252</v>
+        <v>0.753434419631958</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
@@ -1782,28 +1782,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5568.25323312307</v>
+        <v>4562.016395444967</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01444292068481445</v>
+        <v>0.01290750503540039</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>4428.758498256077</v>
+        <v>4439.891390737303</v>
       </c>
       <c r="H37" t="n">
         <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8660497665405273</v>
+        <v>1.061353921890259</v>
       </c>
       <c r="J37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1817,31 +1817,29 @@
           <t>R208</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="C38" t="n">
+        <v>4271.161034760979</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01401615142822266</v>
+        <v>0.01296806335449219</v>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>4192.018395355964</v>
+        <v>4304.29987002672</v>
       </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9710071086883545</v>
+        <v>1.203108310699463</v>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1856,25 +1854,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5802.590206685592</v>
+        <v>6669.834805245112</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01142454147338867</v>
+        <v>0.01143550872802734</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>5553.865715074089</v>
+        <v>4641.58442554471</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>0.555314302444458</v>
+        <v>0.7068057060241699</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
@@ -1892,28 +1890,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6751.544525908008</v>
+        <v>7982.463754360675</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01146626472473145</v>
+        <v>0.01155734062194824</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>5596.082905704381</v>
+        <v>5660.149519821044</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5397136211395264</v>
+        <v>0.744680643081665</v>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1928,28 +1926,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5500.042990675601</v>
+        <v>4370.452077166843</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01467084884643555</v>
+        <v>0.01224660873413086</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>4396.400070107294</v>
+        <v>4490.750467725517</v>
       </c>
       <c r="H41" t="n">
         <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8034927845001221</v>
+        <v>0.9448127746582031</v>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1972,22 +1970,22 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01012277603149414</v>
+        <v>0.009040594100952148</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>20278.29599208476</v>
+        <v>22409.89589700863</v>
       </c>
       <c r="H42" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I42" t="n">
-        <v>0.04027390480041504</v>
+        <v>0.05045223236083984</v>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2010,22 +2008,22 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01037716865539551</v>
+        <v>0.01066255569458008</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>18148.4148668714</v>
+        <v>18048.37350855954</v>
       </c>
       <c r="H43" t="n">
         <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.04753708839416504</v>
+        <v>0.06336021423339844</v>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2048,22 +2046,22 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01111698150634766</v>
+        <v>0.01063680648803711</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>15869.94712523682</v>
+        <v>17974.95640451358</v>
       </c>
       <c r="H44" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.05626845359802246</v>
+        <v>0.07584118843078613</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2086,22 +2084,22 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01131463050842285</v>
+        <v>0.01088619232177734</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>13610.71675456563</v>
+        <v>17932.33127252966</v>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0693356990814209</v>
+        <v>0.08030176162719727</v>
       </c>
       <c r="J45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2124,22 +2122,22 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01067209243774414</v>
+        <v>0.009332895278930664</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>19278.10913891147</v>
+        <v>23426.44102459314</v>
       </c>
       <c r="H46" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I46" t="n">
-        <v>0.04868650436401367</v>
+        <v>0.05415725708007812</v>
       </c>
       <c r="J46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2162,22 +2160,22 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01027560234069824</v>
+        <v>0.009965896606445312</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>17046.07872889366</v>
+        <v>22395.3907924871</v>
       </c>
       <c r="H47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I47" t="n">
-        <v>0.04764890670776367</v>
+        <v>0.06007885932922363</v>
       </c>
       <c r="J47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2200,22 +2198,22 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01154756546020508</v>
+        <v>0.009811878204345703</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>17044.10611528085</v>
+        <v>20126.93388940917</v>
       </c>
       <c r="H48" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.05806851387023926</v>
+        <v>0.06685018539428711</v>
       </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2238,22 +2236,22 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01327133178710938</v>
+        <v>0.0105435848236084</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>14707.52864346469</v>
+        <v>16797.59302944587</v>
       </c>
       <c r="H49" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0716700553894043</v>
+        <v>0.07713437080383301</v>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2268,28 +2266,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8925.341155574679</v>
+        <v>9623.766490013848</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01243281364440918</v>
+        <v>0.01003909111022949</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>7315.592345036148</v>
+        <v>7437.360992985265</v>
       </c>
       <c r="H50" t="n">
         <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2652039527893066</v>
+        <v>0.3128793239593506</v>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2303,29 +2301,31 @@
           <t>RC202</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>8601.013303073547</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.01149630546569824</v>
+        <v>0.01082158088684082</v>
       </c>
       <c r="F51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>5984.180168453855</v>
+        <v>7363.067103435518</v>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3276317119598389</v>
+        <v>0.4546492099761963</v>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2348,19 +2348,19 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01366662979125977</v>
+        <v>0.01145029067993164</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>5764.220240684582</v>
+        <v>5858.200016849487</v>
       </c>
       <c r="H52" t="n">
         <v>4</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4337339401245117</v>
+        <v>0.6280081272125244</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
@@ -2386,22 +2386,22 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.01276254653930664</v>
+        <v>0.01398301124572754</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>5560.310086749476</v>
+        <v>5591.555194414775</v>
       </c>
       <c r="H53" t="n">
         <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>0.712705135345459</v>
+        <v>0.8698368072509766</v>
       </c>
       <c r="J53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2415,31 +2415,29 @@
           <t>RC205</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="C54" t="n">
+        <v>8623.44510183901</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01226186752319336</v>
+        <v>0.0107572078704834</v>
       </c>
       <c r="F54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>7387.208855517321</v>
+        <v>8516.863399779531</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2922725677490234</v>
+        <v>0.3827786445617676</v>
       </c>
       <c r="J54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2453,31 +2451,29 @@
           <t>RC206</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="C55" t="n">
+        <v>7093.10405670561</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01217007637023926</v>
+        <v>0.01099276542663574</v>
       </c>
       <c r="F55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>6023.132768200807</v>
+        <v>6060.670840848993</v>
       </c>
       <c r="H55" t="n">
         <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3490347862243652</v>
+        <v>0.4460470676422119</v>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2491,28 +2487,26 @@
           <t>RC207</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="C56" t="n">
+        <v>7052.221862921664</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>0.01281547546386719</v>
+        <v>0.01265811920166016</v>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>5779.140692958225</v>
+        <v>5891.465429263846</v>
       </c>
       <c r="H56" t="n">
         <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4571378231048584</v>
+        <v>0.542579174041748</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
@@ -2538,22 +2532,22 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01426196098327637</v>
+        <v>0.01218867301940918</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>4472.288968880614</v>
+        <v>5667.284810709966</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6975557804107666</v>
+        <v>0.7314441204071045</v>
       </c>
       <c r="J57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
